--- a/content/01_기획/files/2026-07-14_A2팀_BE_기능명세서_v0.4.xlsx
+++ b/content/01_기획/files/2026-07-14_A2팀_BE_기능명세서_v0.4.xlsx
@@ -1501,7 +1501,7 @@
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>중복 이메일·미인증·미동의 시 완료 차단</t>
+          <t>중복 이메일(Google 가입 이메일 포함)·미인증·미동의 시 완료 차단</t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="M6" s="42" t="inlineStr">
         <is>
-          <t>통합 v0.4 기준 유지</t>
+          <t>07-15 이메일-가입 방식 배타(BE 구현): Google 가입 이메일은 일반 가입 불가</t>
         </is>
       </c>
       <c r="N6" s="42" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="I7" s="42" t="inlineStr">
         <is>
-          <t>OAuth 취소·실패 시 로그인 화면 유지와 오류 표시</t>
+          <t>OAuth 취소·실패 시 로그인 화면 유지와 오류 표시 · 일반 가입 이메일은 Google 가입 차단</t>
         </is>
       </c>
       <c r="J7" s="42" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="M7" s="42" t="inlineStr">
         <is>
-          <t>통합 v0.4 기준 유지</t>
+          <t>07-15 이메일-가입 방식 배타(BE 구현): 일반 가입 이메일은 Google 가입 불가</t>
         </is>
       </c>
       <c r="N7" s="42" t="inlineStr">
@@ -4289,47 +4289,47 @@
       </c>
       <c r="E45" s="48" t="inlineStr">
         <is>
-          <t>Google 계정 연결 관리</t>
+          <t>가입 방식 표시</t>
         </is>
       </c>
       <c r="F45" s="42" t="inlineStr">
         <is>
-          <t>Google 가입 사용자 / 연결 상태·해제</t>
+          <t>로그인 사용자 / 가입 방식 확인</t>
         </is>
       </c>
       <c r="G45" s="42" t="inlineStr">
         <is>
-          <t>가입 방식에 따라 화면 분기 후 연결 관리</t>
+          <t>가입 방식에 따라 화면 분기, 가입 방식(일반/Google) 표시. 연결 추가·해제 없음</t>
         </is>
       </c>
       <c r="H45" s="42" t="inlineStr">
         <is>
-          <t>연결 계정 상태</t>
+          <t>가입 방식 표시</t>
         </is>
       </c>
       <c r="I45" s="42" t="inlineStr">
         <is>
-          <t>유일 로그인 수단 해제 정책 확인</t>
+          <t>가입 방식 배타로 유일 수단 해제 정책 확인 항목 해소</t>
         </is>
       </c>
       <c r="J45" s="42" t="inlineStr">
         <is>
-          <t>Google OAuth·계정 연결 API 미정</t>
+          <t>User 가입 방식 필드 확인</t>
         </is>
       </c>
       <c r="K45" s="42" t="inlineStr">
         <is>
-          <t>Google 사용자에게만 연결 상태와 가능한 액션이 보인다</t>
+          <t>가입 방식이 정확히 표시되고 연결·해제 액션이 노출되지 않는다</t>
         </is>
       </c>
       <c r="L45" s="42" t="inlineStr">
         <is>
-          <t>연결 관리 착수 여부 확인 ❓ (Google 로그인 자체는 AUTH-003)</t>
+          <t>이메일-가입 방식 배타 구현 완료 (로그인 자체는 AUTH-003)</t>
         </is>
       </c>
       <c r="M45" s="42" t="inlineStr">
         <is>
-          <t>개발 이슈·범위 문서 추후 보완</t>
+          <t>07-15 이메일-가입 방식 배타(BE 구현) · 계정 연결·해제 범위 제외</t>
         </is>
       </c>
       <c r="N45" s="42" t="inlineStr">
@@ -4885,17 +4885,17 @@
       </c>
       <c r="B6" s="42" t="inlineStr">
         <is>
-          <t>Google 로그인·연결 관리</t>
+          <t>Google 로그인</t>
         </is>
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
-          <t>OAuth code·연결 액션</t>
+          <t>OAuth code</t>
         </is>
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
-          <t>세션·연결 상태</t>
+          <t>세션·가입 방식</t>
         </is>
       </c>
       <c r="E6" s="42" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
-          <t>로그인과 프로필 연결 API 구분</t>
+          <t>가입 방식 배타 — 연결 관리 API 없음</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="D25" s="42" t="inlineStr">
         <is>
-          <t>Google 연결·탈퇴 범위 정의 필요</t>
+          <t>가입 방식 필드·탈퇴 범위 정의 필요</t>
         </is>
       </c>
       <c r="E25" s="76" t="n"/>

--- a/content/01_기획/files/2026-07-14_A2팀_BE_기능명세서_v0.4.xlsx
+++ b/content/01_기획/files/2026-07-14_A2팀_BE_기능명세서_v0.4.xlsx
@@ -1501,7 +1501,7 @@
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>중복 이메일(Google 가입 이메일 포함)·미인증·미동의 시 완료 차단</t>
+          <t>중복 이메일·미인증·미동의 시 완료 차단</t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="M6" s="42" t="inlineStr">
         <is>
-          <t>07-15 이메일-가입 방식 배타(BE 구현): Google 가입 이메일은 일반 가입 불가</t>
+          <t>통합 v0.4 기준 유지</t>
         </is>
       </c>
       <c r="N6" s="42" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="I7" s="42" t="inlineStr">
         <is>
-          <t>OAuth 취소·실패 시 로그인 화면 유지와 오류 표시 · 일반 가입 이메일은 Google 가입 차단</t>
+          <t>OAuth 취소·실패 시 로그인 화면 유지와 오류 표시</t>
         </is>
       </c>
       <c r="J7" s="42" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="M7" s="42" t="inlineStr">
         <is>
-          <t>07-15 이메일-가입 방식 배타(BE 구현): 일반 가입 이메일은 Google 가입 불가</t>
+          <t>통합 v0.4 기준 유지</t>
         </is>
       </c>
       <c r="N7" s="42" t="inlineStr">
@@ -4289,47 +4289,47 @@
       </c>
       <c r="E45" s="48" t="inlineStr">
         <is>
-          <t>가입 방식 표시</t>
+          <t>Google 계정 연결 관리</t>
         </is>
       </c>
       <c r="F45" s="42" t="inlineStr">
         <is>
-          <t>로그인 사용자 / 가입 방식 확인</t>
+          <t>Google 가입 사용자 / 연결 상태·해제</t>
         </is>
       </c>
       <c r="G45" s="42" t="inlineStr">
         <is>
-          <t>가입 방식에 따라 화면 분기, 가입 방식(일반/Google) 표시. 연결 추가·해제 없음</t>
+          <t>가입 방식에 따라 화면 분기 후 연결 관리</t>
         </is>
       </c>
       <c r="H45" s="42" t="inlineStr">
         <is>
-          <t>가입 방식 표시</t>
+          <t>연결 계정 상태</t>
         </is>
       </c>
       <c r="I45" s="42" t="inlineStr">
         <is>
-          <t>가입 방식 배타로 유일 수단 해제 정책 확인 항목 해소</t>
+          <t>유일 로그인 수단 해제 정책 확인</t>
         </is>
       </c>
       <c r="J45" s="42" t="inlineStr">
         <is>
-          <t>User 가입 방식 필드 확인</t>
+          <t>Google OAuth·계정 연결 API 미정</t>
         </is>
       </c>
       <c r="K45" s="42" t="inlineStr">
         <is>
-          <t>가입 방식이 정확히 표시되고 연결·해제 액션이 노출되지 않는다</t>
+          <t>Google 사용자에게만 연결 상태와 가능한 액션이 보인다</t>
         </is>
       </c>
       <c r="L45" s="42" t="inlineStr">
         <is>
-          <t>이메일-가입 방식 배타 구현 완료 (로그인 자체는 AUTH-003)</t>
+          <t>연결 관리 착수 여부 확인 ❓ (Google 로그인 자체는 AUTH-003)</t>
         </is>
       </c>
       <c r="M45" s="42" t="inlineStr">
         <is>
-          <t>07-15 이메일-가입 방식 배타(BE 구현) · 계정 연결·해제 범위 제외</t>
+          <t>개발 이슈·범위 문서 추후 보완</t>
         </is>
       </c>
       <c r="N45" s="42" t="inlineStr">
@@ -4885,17 +4885,17 @@
       </c>
       <c r="B6" s="42" t="inlineStr">
         <is>
-          <t>Google 로그인</t>
+          <t>Google 로그인·연결 관리</t>
         </is>
       </c>
       <c r="C6" s="42" t="inlineStr">
         <is>
-          <t>OAuth code</t>
+          <t>OAuth code·연결 액션</t>
         </is>
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
-          <t>세션·가입 방식</t>
+          <t>세션·연결 상태</t>
         </is>
       </c>
       <c r="E6" s="42" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
-          <t>가입 방식 배타 — 연결 관리 API 없음</t>
+          <t>로그인과 프로필 연결 API 구분</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="D25" s="42" t="inlineStr">
         <is>
-          <t>가입 방식 필드·탈퇴 범위 정의 필요</t>
+          <t>Google 연결·탈퇴 범위 정의 필요</t>
         </is>
       </c>
       <c r="E25" s="76" t="n"/>
